--- a/scripts/prestadores.xlsx
+++ b/scripts/prestadores.xlsx
@@ -468,11 +468,6 @@
           <t>Latitude/Longitude</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Cadastrado por</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,7 +506,6 @@
           <t>-4.556260796835767, -37.75578076240889</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -550,7 +544,6 @@
           <t>-4.352622446406684, -39.3266264288353</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,7 +582,6 @@
           <t>-5.181518540129727, -40.66450812883529</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -628,7 +620,6 @@
           <t>-3.9351716398247034, -38.50355821534118</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,7 +658,6 @@
           <t>-4.100600675356213, -38.50092545767059</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -706,7 +696,6 @@
           <t>-7.232709156878971, -39.312468913494115</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -745,7 +734,6 @@
           <t>-5.107919230551275, -38.3631534711647</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -784,7 +772,6 @@
           <t>-3.7064713465670556, -40.36118321534118</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -823,7 +810,6 @@
           <t>-3.7448037459114634, -41.009534986505045</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -866,7 +852,6 @@
           <t>-5.0920108, -42.8037597</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -909,7 +894,6 @@
           <t>-1.4227, -48.4695</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -948,7 +932,6 @@
           <t>-2.5758872, -44.2227959</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -991,7 +974,6 @@
           <t>-3.8679887, -38.5101615</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1034,7 +1016,6 @@
           <t>-3.098, -59.970</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1077,7 +1058,6 @@
           <t>-12.850, -38.370</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1120,7 +1100,6 @@
           <t>-16.720, -49.250</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1163,7 +1142,6 @@
           <t>-23.485, -46.735</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1206,7 +1184,6 @@
           <t>-3.821, -38.505</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1249,7 +1226,6 @@
           <t>-3.703, -40.348</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1292,7 +1268,6 @@
           <t>-3.703, -40.348</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1335,7 +1310,6 @@
           <t>-3.703, -40.348</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1378,7 +1352,6 @@
           <t>-3.703, -40.348</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1421,7 +1394,6 @@
           <t>-3.706, -40.351</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1460,7 +1432,6 @@
           <t>-3.712, -40.360</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1503,7 +1474,6 @@
           <t>-3.699, -40.345</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1546,7 +1516,6 @@
           <t>-3.670, -40.320</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1589,7 +1558,6 @@
           <t>-5.0920108, -42.8037597</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1632,7 +1600,6 @@
           <t>-3.098, -59.970</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1675,7 +1642,6 @@
           <t>-12.850, -38.370</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1718,7 +1684,6 @@
           <t>-3.821, -38.505</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1761,7 +1726,6 @@
           <t>-3.746, -40.312</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1804,7 +1768,6 @@
           <t>-3.747, -40.311</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1843,7 +1806,6 @@
           <t>-3.720, -40.331</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1886,7 +1848,6 @@
           <t>-3.710, -40.417</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1929,7 +1890,6 @@
           <t>-2.898, -40.840</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1972,7 +1932,6 @@
           <t>-3.689, -39.811</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2015,7 +1974,6 @@
           <t>-3.689, -39.811</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2058,7 +2016,6 @@
           <t>-3.772, -40.291</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2101,7 +2058,6 @@
           <t>-3.772, -40.291</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2144,7 +2100,6 @@
           <t>-4.941, -37.975</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2187,7 +2142,6 @@
           <t>-5.178, -40.667</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2232,7 +2186,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Print</t>
         </is>
       </c>
     </row>

--- a/scripts/prestadores.xlsx
+++ b/scripts/prestadores.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,11 @@
           <t>Latitude/Longitude</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cadastrado por</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -480,7 +485,6 @@
           <t>OFICINA O CARLINHO E JADERSON CAMINHOES</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>VILA SÃO RAFAEL RUA A - Várzea da Matriz, Aracati - CE, 62800-000</t>
@@ -518,7 +522,6 @@
           <t>VB. Diesel Peças&amp;Serviços</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Av - R. Pres. Geisel, 1816 - Canindezinho, Canindé - CE, 62700-000</t>
@@ -556,7 +559,6 @@
           <t>Oficina Só Diesel</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>R. Moura Fé, 462 - São Vicente, Crateús - CE, 63700-000</t>
@@ -594,7 +596,6 @@
           <t>Deassis Soluções</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>R. Santa Helena, 647 - quadra 47 lote 02 - Jabuti, Eusébio - CE, 61760-000</t>
@@ -632,7 +633,6 @@
           <t>MAC Reboque</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>ROD. SANTOS DUMONT, 4817 KM40 - Centro, Horizonte - CE, 62880-000</t>
@@ -670,7 +670,6 @@
           <t>Borracharia do Biscoito</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Próximo a Nacional Gás - Av. Ailton Gomes - Juazeiro do Norte, CE, 63051-015</t>
@@ -708,7 +707,6 @@
           <t>Auto Elétrica Juazeiro</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Av. Manoel Castro Gomes de Andrade, 1561 - Morada Nova, CE, 62940-000</t>
@@ -746,7 +744,6 @@
           <t>LS Lavajato Caminhões</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Rodovia Br 222 Km 225, Sobral - CE, 62.014-080</t>
@@ -784,7 +781,6 @@
           <t>CATATAU PNEUS: AFERIÇÃO E MANUTENÇÃO DE TACÓGRAFOS.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>BR-222, KM 315 - Gov. Ferraz, Tianguá - CE, 62320-000</t>
@@ -906,7 +902,6 @@
           <t>Oficina Mecanica GPE</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Av. Três, 6 - quadra 231 - Jardim São Cristovão, São Luís - MA, 65055-315</t>
@@ -1416,7 +1411,6 @@
           <t>BR 222 Faz Ipueiras Km 244, Sn Zona Rural, BR-222 - Gerardo Cristino, Sobral - CE, 62100-000</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Sobral</t>
@@ -1688,32 +1682,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ponto de Apoio</t>
+          <t>Borracharia</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Auto Posto Gatão</t>
+          <t>Borracharia Central</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Posto 24h com amplo estacionamento pra caminhão, restaurante, banho e pousada anexa</t>
+          <t>Venda de pneus e aros</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BR-222, KM 218, Sobral - CE, 62103-000</t>
+          <t>R. Bandeirantes, 379 - Camocim, CE, 62400-000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(88) 99910-1097</t>
+          <t>(88) 98197-5313</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sobral</t>
+          <t>Camocim</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1723,39 +1717,39 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-3.746, -40.312</t>
+          <t>-2.898, -40.840</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ponto de Apoio</t>
+          <t>Borracharia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hotel Gatão - Sobral</t>
+          <t>Santa Maria Borracharia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pousada na beira da BR-222 anexa ao posto, café da manhã e estacionamento pra caminhão</t>
+          <t>Conserto e troca de pneus, montagem sem câmara, vulcanização, elétrica em geral, venda de acessórios - pátio do Posto Icar, BR-222</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BR-222, KM 219, Sobral - CE, 62103-000</t>
+          <t>BR-222, Posto Icar, Iraucuba - CE, 62150-000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(88) 99216-4421</t>
+          <t>(85) 98575-1978</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sobral</t>
+          <t>Iraucuba</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1765,35 +1759,39 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-3.747, -40.311</t>
+          <t>-3.689, -39.811</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ponto de Apoio</t>
+          <t>Elétrica</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Posto Shell</t>
+          <t>Santa Maria Borracharia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Posto 24h com área de parada pra caminhoneiro na BR-222</t>
+          <t>Conserto e troca de pneus, montagem sem câmara, vulcanização, elétrica em geral, venda de acessórios - pátio do Posto Icar, BR-222</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BR 222 Faz Ipueiras Km 244, Sn Zona Rural, BR-222 - Gerardo Cristino, Sobral - CE, 62100-000</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>BR-222, Posto Icar, Iraucuba - CE, 62150-000</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(85) 98575-1978</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sobral</t>
+          <t>Iraucuba</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1803,39 +1801,39 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-3.720, -40.331</t>
+          <t>-3.689, -39.811</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ponto de Apoio</t>
+          <t>Mecânico</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Posto São Domingos Jaburuna</t>
+          <t>Oficina e Borracharia AB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Posto 24h com conveniência e oficina, ponto de parada na BR-222</t>
+          <t>Oficina de caminhões e borracharia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BR-222, 232 - Jaburuna, Sobral - CE, 62100-000</t>
+          <t>Av. José Raimundo de Loiola - Edmundo Rodrigues, Forquilha - CE, 62115-000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(88) 3611-4242</t>
+          <t>(88) 99206-0860</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sobral</t>
+          <t>Forquilha</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1845,7 +1843,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-3.710, -40.417</t>
+          <t>-3.772, -40.291</t>
         </is>
       </c>
     </row>
@@ -1857,27 +1855,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Borracharia Central</t>
+          <t>Oficina e Borracharia AB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Venda de pneus e aros</t>
+          <t>Oficina de caminhões e borracharia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R. Bandeirantes, 379 - Camocim, CE, 62400-000</t>
+          <t>Av. José Raimundo de Loiola - Edmundo Rodrigues, Forquilha - CE, 62115-000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(88) 98197-5313</t>
+          <t>(88) 99206-0860</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Camocim</t>
+          <t>Forquilha</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1887,7 +1885,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-2.898, -40.840</t>
+          <t>-3.772, -40.291</t>
         </is>
       </c>
     </row>
@@ -1899,27 +1897,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Santa Maria Borracharia</t>
+          <t>Borracharia O Vilson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Conserto e troca de pneus, montagem sem câmara, vulcanização, elétrica em geral, venda de acessórios - pátio do Posto Icar, BR-222</t>
+          <t>Vulcanização de todos os tipos, atendimento ágil, aceita cartão de crédito e Pix - em frente ao Auto Posto Granville</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BR-222, Posto Icar, Iraucuba - CE, 62150-000</t>
+          <t>Em frente ao Auto Posto Granville, Russas - CE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(85) 98575-1978</t>
+          <t>(88) 99674-7478</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Iraucuba</t>
+          <t>Russas</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1929,39 +1927,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-3.689, -39.811</t>
+          <t>-4.941, -37.975</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Elétrica</t>
+          <t>Borracharia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Santa Maria Borracharia</t>
+          <t>Borracharia móvel Gilliard 24 horas</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Conserto e troca de pneus, montagem sem câmara, vulcanização, elétrica em geral, venda de acessórios - pátio do Posto Icar, BR-222</t>
+          <t>Borracharia móvel, atendimento 24 horas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BR-222, Posto Icar, Iraucuba - CE, 62150-000</t>
+          <t>Tv. Eduardo Albuquerque, 14 - Venâncio, Crateús - CE, 63700-000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(85) 98575-1978</t>
+          <t>(88) 99404-5162</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Iraucuba</t>
+          <t>Crateús</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1971,220 +1969,52 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-3.689, -39.811</t>
+          <t>-5.178, -40.667</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mecânico</t>
+          <t>Lava-Jato</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Oficina e Borracharia AB</t>
+          <t>LavajatoJk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Oficina de caminhões e borracharia</t>
+          <t>Lavagem de caminhões e carretas</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Av. José Raimundo de Loiola - Edmundo Rodrigues, Forquilha - CE, 62115-000</t>
+          <t>BR-135, KM 262 - Alvorada do Gurguéia - PI, 64923-000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(88) 99206-0860</t>
+          <t>(89) 98115-5132</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Forquilha</t>
+          <t>Alvorada do Gurguéia</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-3.772, -40.291</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Borracharia</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Oficina e Borracharia AB</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Oficina de caminhões e borracharia</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Av. José Raimundo de Loiola - Edmundo Rodrigues, Forquilha - CE, 62115-000</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>(88) 99206-0860</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Forquilha</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-3.772, -40.291</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Borracharia</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Borracharia O Vilson</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Vulcanização de todos os tipos, atendimento ágil, aceita cartão de crédito e Pix - em frente ao Auto Posto Granville</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Em frente ao Auto Posto Granville, Russas - CE</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>(88) 99674-7478</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Russas</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-4.941, -37.975</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Borracharia</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Borracharia móvel Gilliard 24 horas</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Borracharia móvel, atendimento 24 horas</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Tv. Eduardo Albuquerque, 14 - Venâncio, Crateús - CE, 63700-000</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>(88) 99404-5162</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Crateús</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-5.178, -40.667</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Lava-Jato</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>LavajatoJk</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Lavagem de caminhões e carretas</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>BR-135, KM 262 - Alvorada do Gurguéia - PI, 64923-000</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>(89) 98115-5132</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Alvorada do Gurguéia</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
           <t>-8.442, -43.858</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Print</t>
         </is>

--- a/scripts/prestadores.xlsx
+++ b/scripts/prestadores.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -2020,6 +2020,53 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Funilaria</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JR Lanternagem | Linha Pesada</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Especialista na linha truck - funilaria, lanternagem e pintura para caminhões, tratores e máquinas pesadas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Parnamirim - RN</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>(84) 99144-6490</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Parnamirim</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-5.9308, -35.2581</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
